--- a/tabela dimenscional.xlsx
+++ b/tabela dimenscional.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\labsfiap\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEDD9F47-59F6-484D-8A7B-16B01C3C1890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7A1050-4027-4FEF-BA7C-219D59B08577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{832D3EDC-D548-4031-85E3-C01272E93F60}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{832D3EDC-D548-4031-85E3-C01272E93F60}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabela Dimensional" sheetId="1" r:id="rId1"/>
+    <sheet name="Cotação" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t>Componente</t>
   </si>
@@ -138,13 +139,70 @@
   </si>
   <si>
     <t>Fixação por parafusos ao chassi</t>
+  </si>
+  <si>
+    <t>ESP32 30 pinos</t>
+  </si>
+  <si>
+    <t>Cabo Micro USB</t>
+  </si>
+  <si>
+    <t>Ponte H L298N</t>
+  </si>
+  <si>
+    <t>Kit 60 jumpers</t>
+  </si>
+  <si>
+    <t>HC-SR04</t>
+  </si>
+  <si>
+    <t>2 baterias 18650</t>
+  </si>
+  <si>
+    <t>Suporte duplo 18650</t>
+  </si>
+  <si>
+    <t>Chassi 2WD completo</t>
+  </si>
+  <si>
+    <t>Mini protoboard</t>
+  </si>
+  <si>
+    <t>MDF 30×30 cm, 3 mm</t>
+  </si>
+  <si>
+    <t>Itens</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Loja</t>
+  </si>
+  <si>
+    <t>Eletrogate</t>
+  </si>
+  <si>
+    <t>Casadarobotica</t>
+  </si>
+  <si>
+    <t>Genesisrobotec</t>
+  </si>
+  <si>
+    <t>Mercadolivre</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="_([$BRL]\ * #,##0.00_);_([$BRL]\ * \(#,##0.00\);_([$BRL]\ * &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,6 +218,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -170,18 +236,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -204,11 +270,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -217,9 +310,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -234,8 +324,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -579,25 +694,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2" t="str">
@@ -617,7 +732,7 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -634,7 +749,7 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -651,7 +766,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -668,7 +783,7 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -685,7 +800,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -702,7 +817,7 @@
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -714,38 +829,201 @@
       <c r="D8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N9" s="7"/>
-      <c r="O9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="5"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N10" s="7"/>
-      <c r="O10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="5"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N11" s="7"/>
-      <c r="O11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="5"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N12" s="7"/>
-      <c r="O12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="5"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N13" s="7"/>
-      <c r="O13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="5"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N14" s="7"/>
-      <c r="O14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04EC1066-C2DB-40B7-BE57-B5524B17E389}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="10">
+        <v>44.85</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="10">
+        <v>4.99</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="10">
+        <v>4.96</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="10">
+        <v>15.99</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="10">
+        <v>9.9</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="10">
+        <f>20.5*2</f>
+        <v>41</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="10">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="10">
+        <v>54.99</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="10">
+        <v>3.49</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="10">
+        <v>32.79</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="13">
+        <f>SUM(B2:B11)</f>
+        <v>217.86</v>
+      </c>
+      <c r="C12" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B12:C12"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{15319800-4F82-4CC6-A949-B44F37AC159A}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{D16D1BF1-4FBE-4038-AD72-8E2A6D04118A}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{AF2A02C3-D211-40AE-8204-0DE29DAB5B8B}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{3BB8CAEC-536A-4420-9F61-1C374D29A3BA}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{36DF57BC-545D-4A32-8579-A16A8EC3CC00}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{5DB915E7-74A3-4039-8FC2-F31EF7F7E3F3}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{5CE6EE98-8809-4962-A661-A64EB62241E9}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{35AD4C47-4421-4D61-A894-86D29F2189B9}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{0AA5F3B6-28FB-4AC7-9CC2-42B838CDA609}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{4FFA8D92-8814-4289-AC72-8EDF86FF7095}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId11"/>
+</worksheet>
 </file>